--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.25954317031161</v>
+        <v>7.029675765175637</v>
       </c>
       <c r="D2" t="n">
-        <v>43.17047395364749</v>
+        <v>7.015202017467717</v>
       </c>
       <c r="E2" t="n">
-        <v>10.8524570629797</v>
+        <v>1.763524272734202</v>
       </c>
       <c r="F2" t="n">
-        <v>10.8604061453206</v>
+        <v>1.764815998614597</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.73342944938565</v>
+        <v>9.056682285525168</v>
       </c>
       <c r="D3" t="n">
-        <v>55.62421891358104</v>
+        <v>9.03893557345692</v>
       </c>
       <c r="E3" t="n">
-        <v>10.8524570629797</v>
+        <v>1.763524272734202</v>
       </c>
       <c r="F3" t="n">
-        <v>10.8604061453206</v>
+        <v>1.764815998614597</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.2791005837445</v>
+        <v>4.107853844858482</v>
       </c>
       <c r="D4" t="n">
-        <v>25.13116557996282</v>
+        <v>4.083814406743958</v>
       </c>
       <c r="E4" t="n">
-        <v>10.8524570629797</v>
+        <v>1.763524272734202</v>
       </c>
       <c r="F4" t="n">
-        <v>10.8604061453206</v>
+        <v>1.764815998614597</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.66655267201333</v>
+        <v>6.445814809202167</v>
       </c>
       <c r="D5" t="n">
-        <v>39.81160794663461</v>
+        <v>6.469386291328124</v>
       </c>
       <c r="E5" t="n">
-        <v>10.8524570629797</v>
+        <v>1.763524272734202</v>
       </c>
       <c r="F5" t="n">
-        <v>10.8604061453206</v>
+        <v>1.764815998614597</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
